--- a/Docs/QA-Testing/Test_Case_StateTransition.xlsx
+++ b/Docs/QA-Testing/Test_Case_StateTransition.xlsx
@@ -1,16 +1,16 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="10909"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="29127"/>
   <workbookPr/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="/Users/admin/Downloads/Online-Store/Docs/QA-Testing/"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\KiemChungPhanMem\Docs\QA-Testing\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{97960FBD-34D8-DD47-B99E-E3585D9D365D}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{DF9FA335-A7EE-4C6E-8928-E1C803337FEA}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="0" yWindow="0" windowWidth="33600" windowHeight="21000" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="12456" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="State Transition Test Cases" sheetId="1" r:id="rId1"/>
@@ -23,7 +23,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="227" uniqueCount="137">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="222" uniqueCount="134">
   <si>
     <t>TC ID</t>
   </si>
@@ -361,9 +361,6 @@
     <t>HTTP 200, Empty cart</t>
   </si>
   <si>
-    <t>Ở người dùng Guest, khi xóa sản phẩm khỏi giỏ hàng thì có thể ra lại trang chủ tìm SP khác</t>
-  </si>
-  <si>
     <t>TC-ST-15</t>
   </si>
   <si>
@@ -403,9 +400,6 @@
     <t>DELETE</t>
   </si>
   <si>
-    <t>CẦN CHẠY LẠI ĐỂ XÁC NHẬN — dự đoán theo code: HTTP 500 (NullPointerException chưa được catch trong deleteItem(), khác với addToCart() có try-catch)</t>
-  </si>
-  <si>
     <t>HTTP 403 Forbidden</t>
   </si>
   <si>
@@ -427,20 +421,17 @@
     <t>Tỉnh trạng(RECHECK)</t>
   </si>
   <si>
-    <t>NOTE</t>
-  </si>
-  <si>
-    <t>THANH</t>
-  </si>
-  <si>
-    <t>THÙY</t>
+    <t>HTTP 401 Unauthorized (Guest không được thao tác /cart/**)</t>
+  </si>
+  <si>
+    <t>Security Filter chặn trước controller; không còn NPE/500</t>
   </si>
 </sst>
 </file>
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="x14ac x16r2 xr">
-  <fonts count="4" x14ac:knownFonts="1">
+  <fonts count="3" x14ac:knownFonts="1">
     <font>
       <sz val="11"/>
       <color theme="1"/>
@@ -450,19 +441,13 @@
     </font>
     <font>
       <b/>
-      <sz val="11"/>
+      <sz val="12"/>
       <color rgb="FFFFFFFF"/>
       <name val="Times New Roman"/>
       <family val="1"/>
     </font>
     <font>
-      <sz val="11"/>
-      <color theme="1"/>
-      <name val="Times New Roman"/>
-      <family val="1"/>
-    </font>
-    <font>
-      <sz val="10"/>
+      <sz val="12"/>
       <color theme="1"/>
       <name val="Times New Roman"/>
       <family val="1"/>
@@ -556,6 +541,9 @@
     <xf numFmtId="0" fontId="1" fillId="2" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment vertical="top" wrapText="1"/>
     </xf>
+    <xf numFmtId="0" fontId="2" fillId="8" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="top" wrapText="1"/>
+    </xf>
     <xf numFmtId="0" fontId="2" fillId="3" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
@@ -565,10 +553,19 @@
     <xf numFmtId="0" fontId="2" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment vertical="top" wrapText="1"/>
     </xf>
+    <xf numFmtId="0" fontId="2" fillId="8" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="7" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
     <xf numFmtId="0" fontId="2" fillId="4" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment vertical="top" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="3" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="2" fillId="8" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="2" fillId="6" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
@@ -582,18 +579,6 @@
     </xf>
     <xf numFmtId="0" fontId="2" fillId="5" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="7" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="8" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="8" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="top" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="8" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="2" fillId="9" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
@@ -900,26 +885,26 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
-  <dimension ref="A1:O16"/>
-  <sheetFormatPr baseColWidth="10" defaultColWidth="8.83203125" defaultRowHeight="15" outlineLevelCol="1" x14ac:dyDescent="0.2"/>
+  <dimension ref="A1:N16"/>
+  <sheetFormatPr defaultColWidth="8.77734375" defaultRowHeight="14.4" outlineLevelCol="1" x14ac:dyDescent="0.3"/>
   <cols>
-    <col min="1" max="1" width="9.5" bestFit="1" customWidth="1"/>
-    <col min="2" max="2" width="35.1640625" bestFit="1" customWidth="1"/>
-    <col min="3" max="3" width="39.5" bestFit="1" customWidth="1" outlineLevel="1"/>
-    <col min="4" max="4" width="29.1640625" bestFit="1" customWidth="1" outlineLevel="1"/>
-    <col min="5" max="5" width="16.83203125" bestFit="1" customWidth="1" outlineLevel="1"/>
-    <col min="6" max="6" width="16.5" bestFit="1" customWidth="1" outlineLevel="1"/>
-    <col min="7" max="7" width="10.5" bestFit="1" customWidth="1" outlineLevel="1"/>
-    <col min="8" max="8" width="17.83203125" bestFit="1" customWidth="1" outlineLevel="1"/>
-    <col min="9" max="9" width="30" customWidth="1"/>
-    <col min="10" max="10" width="40" customWidth="1"/>
-    <col min="11" max="11" width="14.6640625" bestFit="1" customWidth="1"/>
-    <col min="12" max="12" width="10.5" bestFit="1" customWidth="1"/>
-    <col min="13" max="13" width="44.83203125" bestFit="1" customWidth="1"/>
-    <col min="14" max="14" width="21.6640625" customWidth="1"/>
+    <col min="1" max="1" width="9.109375" bestFit="1" customWidth="1"/>
+    <col min="2" max="2" width="34.5546875" bestFit="1" customWidth="1"/>
+    <col min="3" max="3" width="39.33203125" bestFit="1" customWidth="1" outlineLevel="1"/>
+    <col min="4" max="4" width="27.77734375" bestFit="1" customWidth="1" outlineLevel="1"/>
+    <col min="5" max="5" width="14.6640625" bestFit="1" customWidth="1" outlineLevel="1"/>
+    <col min="6" max="6" width="16.44140625" bestFit="1" customWidth="1" outlineLevel="1"/>
+    <col min="7" max="7" width="10.44140625" bestFit="1" customWidth="1" outlineLevel="1"/>
+    <col min="8" max="8" width="17.33203125" bestFit="1" customWidth="1" outlineLevel="1"/>
+    <col min="9" max="9" width="29.88671875" bestFit="1" customWidth="1"/>
+    <col min="10" max="10" width="39.77734375" bestFit="1" customWidth="1"/>
+    <col min="11" max="11" width="13" bestFit="1" customWidth="1"/>
+    <col min="12" max="12" width="9.77734375" bestFit="1" customWidth="1"/>
+    <col min="13" max="13" width="44.6640625" bestFit="1" customWidth="1"/>
+    <col min="14" max="14" width="18.5546875" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:15" ht="30" x14ac:dyDescent="0.2">
+    <row r="1" spans="1:14" ht="31.2" x14ac:dyDescent="0.3">
       <c r="A1" s="1" t="s">
         <v>0</v>
       </c>
@@ -960,677 +945,662 @@
         <v>12</v>
       </c>
       <c r="N1" s="1" t="s">
+        <v>131</v>
+      </c>
+    </row>
+    <row r="2" spans="1:14" ht="31.2" x14ac:dyDescent="0.3">
+      <c r="A2" s="2" t="s">
+        <v>13</v>
+      </c>
+      <c r="B2" s="2" t="s">
+        <v>14</v>
+      </c>
+      <c r="C2" s="2" t="s">
+        <v>15</v>
+      </c>
+      <c r="D2" s="2" t="s">
+        <v>16</v>
+      </c>
+      <c r="E2" s="2" t="s">
+        <v>17</v>
+      </c>
+      <c r="F2" s="2" t="s">
+        <v>18</v>
+      </c>
+      <c r="G2" s="2" t="s">
+        <v>19</v>
+      </c>
+      <c r="H2" s="2" t="s">
+        <v>20</v>
+      </c>
+      <c r="I2" s="2" t="s">
+        <v>21</v>
+      </c>
+      <c r="J2" s="2" t="s">
+        <v>22</v>
+      </c>
+      <c r="K2" s="3" t="s">
+        <v>23</v>
+      </c>
+      <c r="L2" s="4" t="s">
+        <v>24</v>
+      </c>
+      <c r="M2" s="2" t="s">
+        <v>25</v>
+      </c>
+      <c r="N2" s="3" t="s">
+        <v>23</v>
+      </c>
+    </row>
+    <row r="3" spans="1:14" ht="31.2" x14ac:dyDescent="0.3">
+      <c r="A3" s="4" t="s">
+        <v>26</v>
+      </c>
+      <c r="B3" s="5" t="s">
+        <v>27</v>
+      </c>
+      <c r="C3" s="5" t="s">
+        <v>28</v>
+      </c>
+      <c r="D3" s="5" t="s">
+        <v>29</v>
+      </c>
+      <c r="E3" s="5" t="s">
+        <v>30</v>
+      </c>
+      <c r="F3" s="5" t="s">
+        <v>31</v>
+      </c>
+      <c r="G3" s="5" t="s">
+        <v>19</v>
+      </c>
+      <c r="H3" s="5" t="s">
+        <v>20</v>
+      </c>
+      <c r="I3" s="5" t="s">
+        <v>32</v>
+      </c>
+      <c r="J3" s="5" t="s">
+        <v>32</v>
+      </c>
+      <c r="K3" s="3" t="s">
+        <v>23</v>
+      </c>
+      <c r="L3" s="4" t="s">
+        <v>24</v>
+      </c>
+      <c r="M3" s="5" t="s">
+        <v>33</v>
+      </c>
+      <c r="N3" s="3" t="s">
+        <v>23</v>
+      </c>
+    </row>
+    <row r="4" spans="1:14" ht="78" x14ac:dyDescent="0.3">
+      <c r="A4" s="6" t="s">
+        <v>34</v>
+      </c>
+      <c r="B4" s="2" t="s">
+        <v>35</v>
+      </c>
+      <c r="C4" s="2" t="s">
+        <v>36</v>
+      </c>
+      <c r="D4" s="2" t="s">
+        <v>37</v>
+      </c>
+      <c r="E4" s="2" t="s">
+        <v>30</v>
+      </c>
+      <c r="F4" s="2" t="s">
+        <v>31</v>
+      </c>
+      <c r="G4" s="2" t="s">
+        <v>19</v>
+      </c>
+      <c r="H4" s="2" t="s">
+        <v>20</v>
+      </c>
+      <c r="I4" s="2" t="s">
+        <v>38</v>
+      </c>
+      <c r="J4" s="2" t="s">
+        <v>39</v>
+      </c>
+      <c r="K4" s="7" t="s">
+        <v>40</v>
+      </c>
+      <c r="L4" s="8" t="s">
+        <v>41</v>
+      </c>
+      <c r="M4" s="9" t="s">
+        <v>42</v>
+      </c>
+      <c r="N4" s="3" t="s">
+        <v>23</v>
+      </c>
+    </row>
+    <row r="5" spans="1:14" ht="62.4" x14ac:dyDescent="0.3">
+      <c r="A5" s="4" t="s">
+        <v>43</v>
+      </c>
+      <c r="B5" s="5" t="s">
+        <v>44</v>
+      </c>
+      <c r="C5" s="5" t="s">
+        <v>45</v>
+      </c>
+      <c r="D5" s="5" t="s">
+        <v>46</v>
+      </c>
+      <c r="E5" s="5" t="s">
+        <v>30</v>
+      </c>
+      <c r="F5" s="5" t="s">
+        <v>18</v>
+      </c>
+      <c r="G5" s="5" t="s">
+        <v>19</v>
+      </c>
+      <c r="H5" s="5" t="s">
+        <v>20</v>
+      </c>
+      <c r="I5" s="5" t="s">
+        <v>38</v>
+      </c>
+      <c r="J5" s="5" t="s">
+        <v>47</v>
+      </c>
+      <c r="K5" s="7" t="s">
+        <v>40</v>
+      </c>
+      <c r="L5" s="8" t="s">
+        <v>41</v>
+      </c>
+      <c r="M5" s="10" t="s">
+        <v>48</v>
+      </c>
+      <c r="N5" s="3" t="s">
+        <v>23</v>
+      </c>
+    </row>
+    <row r="6" spans="1:14" ht="78" x14ac:dyDescent="0.3">
+      <c r="A6" s="6" t="s">
+        <v>49</v>
+      </c>
+      <c r="B6" s="2" t="s">
+        <v>50</v>
+      </c>
+      <c r="C6" s="2" t="s">
+        <v>51</v>
+      </c>
+      <c r="D6" s="2" t="s">
+        <v>52</v>
+      </c>
+      <c r="E6" s="2" t="s">
+        <v>17</v>
+      </c>
+      <c r="F6" s="2" t="s">
+        <v>18</v>
+      </c>
+      <c r="G6" s="2" t="s">
+        <v>53</v>
+      </c>
+      <c r="H6" s="2" t="s">
+        <v>20</v>
+      </c>
+      <c r="I6" s="2" t="s">
+        <v>54</v>
+      </c>
+      <c r="J6" s="2" t="s">
+        <v>55</v>
+      </c>
+      <c r="K6" s="7" t="s">
+        <v>40</v>
+      </c>
+      <c r="L6" s="8" t="s">
+        <v>41</v>
+      </c>
+      <c r="M6" s="2" t="s">
+        <v>56</v>
+      </c>
+      <c r="N6" s="3" t="s">
+        <v>23</v>
+      </c>
+    </row>
+    <row r="7" spans="1:14" ht="31.2" x14ac:dyDescent="0.3">
+      <c r="A7" s="4" t="s">
+        <v>57</v>
+      </c>
+      <c r="B7" s="10" t="s">
+        <v>58</v>
+      </c>
+      <c r="C7" s="5" t="s">
+        <v>59</v>
+      </c>
+      <c r="D7" s="5" t="s">
+        <v>60</v>
+      </c>
+      <c r="E7" s="5" t="s">
+        <v>61</v>
+      </c>
+      <c r="F7" s="5" t="s">
+        <v>31</v>
+      </c>
+      <c r="G7" s="5" t="s">
+        <v>19</v>
+      </c>
+      <c r="H7" s="5" t="s">
+        <v>20</v>
+      </c>
+      <c r="I7" s="5" t="s">
+        <v>125</v>
+      </c>
+      <c r="J7" s="5" t="s">
+        <v>125</v>
+      </c>
+      <c r="K7" s="3" t="s">
+        <v>23</v>
+      </c>
+      <c r="L7" s="4" t="s">
+        <v>24</v>
+      </c>
+      <c r="M7" s="5" t="s">
+        <v>126</v>
+      </c>
+      <c r="N7" s="3" t="s">
+        <v>23</v>
+      </c>
+    </row>
+    <row r="8" spans="1:14" ht="46.8" x14ac:dyDescent="0.3">
+      <c r="A8" s="6" t="s">
+        <v>63</v>
+      </c>
+      <c r="B8" s="2" t="s">
+        <v>64</v>
+      </c>
+      <c r="C8" s="2" t="s">
+        <v>59</v>
+      </c>
+      <c r="D8" s="2" t="s">
+        <v>16</v>
+      </c>
+      <c r="E8" s="2" t="s">
+        <v>65</v>
+      </c>
+      <c r="F8" s="2" t="s">
+        <v>18</v>
+      </c>
+      <c r="G8" s="2" t="s">
+        <v>19</v>
+      </c>
+      <c r="H8" s="2" t="s">
+        <v>20</v>
+      </c>
+      <c r="I8" s="2" t="s">
+        <v>66</v>
+      </c>
+      <c r="J8" s="2" t="s">
+        <v>66</v>
+      </c>
+      <c r="K8" s="3" t="s">
+        <v>23</v>
+      </c>
+      <c r="L8" s="4" t="s">
+        <v>24</v>
+      </c>
+      <c r="M8" s="2" t="s">
+        <v>67</v>
+      </c>
+      <c r="N8" s="3" t="s">
+        <v>23</v>
+      </c>
+    </row>
+    <row r="9" spans="1:14" ht="46.8" x14ac:dyDescent="0.3">
+      <c r="A9" s="4" t="s">
+        <v>68</v>
+      </c>
+      <c r="B9" s="5" t="s">
+        <v>69</v>
+      </c>
+      <c r="C9" s="5" t="s">
+        <v>59</v>
+      </c>
+      <c r="D9" s="5" t="s">
+        <v>70</v>
+      </c>
+      <c r="E9" s="5" t="s">
+        <v>71</v>
+      </c>
+      <c r="F9" s="5" t="s">
+        <v>18</v>
+      </c>
+      <c r="G9" s="5" t="s">
+        <v>19</v>
+      </c>
+      <c r="H9" s="5" t="s">
+        <v>20</v>
+      </c>
+      <c r="I9" s="5" t="s">
+        <v>62</v>
+      </c>
+      <c r="J9" s="5" t="s">
+        <v>72</v>
+      </c>
+      <c r="K9" s="3" t="s">
+        <v>23</v>
+      </c>
+      <c r="L9" s="4" t="s">
+        <v>24</v>
+      </c>
+      <c r="M9" s="5" t="s">
+        <v>73</v>
+      </c>
+      <c r="N9" s="3" t="s">
+        <v>23</v>
+      </c>
+    </row>
+    <row r="10" spans="1:14" ht="46.8" x14ac:dyDescent="0.3">
+      <c r="A10" s="11" t="s">
+        <v>74</v>
+      </c>
+      <c r="B10" s="12" t="s">
+        <v>127</v>
+      </c>
+      <c r="C10" s="12" t="s">
+        <v>75</v>
+      </c>
+      <c r="D10" s="12" t="s">
+        <v>76</v>
+      </c>
+      <c r="E10" s="12" t="s">
+        <v>77</v>
+      </c>
+      <c r="F10" s="12" t="s">
+        <v>117</v>
+      </c>
+      <c r="G10" s="12" t="s">
+        <v>78</v>
+      </c>
+      <c r="H10" s="12" t="s">
+        <v>118</v>
+      </c>
+      <c r="I10" s="12" t="s">
+        <v>62</v>
+      </c>
+      <c r="J10" s="12" t="s">
+        <v>62</v>
+      </c>
+      <c r="K10" s="3" t="s">
+        <v>23</v>
+      </c>
+      <c r="L10" s="4" t="s">
+        <v>24</v>
+      </c>
+      <c r="M10" s="12" t="s">
+        <v>128</v>
+      </c>
+      <c r="N10" s="3" t="s">
+        <v>23</v>
+      </c>
+    </row>
+    <row r="11" spans="1:14" ht="46.8" x14ac:dyDescent="0.3">
+      <c r="A11" s="4" t="s">
+        <v>79</v>
+      </c>
+      <c r="B11" s="13" t="s">
+        <v>80</v>
+      </c>
+      <c r="C11" s="13" t="s">
+        <v>81</v>
+      </c>
+      <c r="D11" s="13" t="s">
+        <v>82</v>
+      </c>
+      <c r="E11" s="13" t="s">
+        <v>60</v>
+      </c>
+      <c r="F11" s="14" t="s">
+        <v>117</v>
+      </c>
+      <c r="G11" s="14" t="s">
+        <v>78</v>
+      </c>
+      <c r="H11" s="14" t="s">
+        <v>119</v>
+      </c>
+      <c r="I11" s="13" t="s">
+        <v>83</v>
+      </c>
+      <c r="J11" s="13" t="s">
+        <v>84</v>
+      </c>
+      <c r="K11" s="3" t="s">
+        <v>23</v>
+      </c>
+      <c r="L11" s="4" t="s">
+        <v>24</v>
+      </c>
+      <c r="M11" s="13" t="s">
+        <v>85</v>
+      </c>
+      <c r="N11" s="3" t="s">
+        <v>23</v>
+      </c>
+    </row>
+    <row r="12" spans="1:14" ht="78" x14ac:dyDescent="0.3">
+      <c r="A12" s="11" t="s">
+        <v>86</v>
+      </c>
+      <c r="B12" s="12" t="s">
+        <v>87</v>
+      </c>
+      <c r="C12" s="12" t="s">
+        <v>88</v>
+      </c>
+      <c r="D12" s="12" t="s">
+        <v>89</v>
+      </c>
+      <c r="E12" s="12" t="s">
+        <v>90</v>
+      </c>
+      <c r="F12" s="12" t="s">
+        <v>120</v>
+      </c>
+      <c r="G12" s="12" t="s">
+        <v>78</v>
+      </c>
+      <c r="H12" s="12" t="s">
+        <v>121</v>
+      </c>
+      <c r="I12" s="12" t="s">
+        <v>91</v>
+      </c>
+      <c r="J12" s="12" t="s">
+        <v>92</v>
+      </c>
+      <c r="K12" s="3" t="s">
+        <v>23</v>
+      </c>
+      <c r="L12" s="4" t="s">
+        <v>24</v>
+      </c>
+      <c r="M12" s="12" t="s">
+        <v>93</v>
+      </c>
+      <c r="N12" s="3" t="s">
+        <v>23</v>
+      </c>
+    </row>
+    <row r="13" spans="1:14" ht="31.2" x14ac:dyDescent="0.3">
+      <c r="A13" s="4" t="s">
+        <v>94</v>
+      </c>
+      <c r="B13" s="13" t="s">
+        <v>95</v>
+      </c>
+      <c r="C13" s="13" t="s">
+        <v>96</v>
+      </c>
+      <c r="D13" s="13" t="s">
+        <v>97</v>
+      </c>
+      <c r="E13" s="13" t="s">
+        <v>60</v>
+      </c>
+      <c r="F13" s="14" t="s">
+        <v>122</v>
+      </c>
+      <c r="G13" s="14" t="s">
+        <v>78</v>
+      </c>
+      <c r="H13" s="14" t="s">
+        <v>98</v>
+      </c>
+      <c r="I13" s="14" t="s">
+        <v>99</v>
+      </c>
+      <c r="J13" s="14" t="s">
+        <v>99</v>
+      </c>
+      <c r="K13" s="3" t="s">
+        <v>23</v>
+      </c>
+      <c r="L13" s="4" t="s">
+        <v>24</v>
+      </c>
+      <c r="M13" s="13" t="s">
+        <v>100</v>
+      </c>
+      <c r="N13" s="3" t="s">
+        <v>23</v>
+      </c>
+    </row>
+    <row r="14" spans="1:14" ht="46.8" x14ac:dyDescent="0.3">
+      <c r="A14" s="11" t="s">
+        <v>101</v>
+      </c>
+      <c r="B14" s="12" t="s">
+        <v>102</v>
+      </c>
+      <c r="C14" s="12" t="s">
+        <v>103</v>
+      </c>
+      <c r="D14" s="12" t="s">
+        <v>104</v>
+      </c>
+      <c r="E14" s="12" t="s">
+        <v>60</v>
+      </c>
+      <c r="F14" s="12" t="s">
+        <v>122</v>
+      </c>
+      <c r="G14" s="12" t="s">
+        <v>78</v>
+      </c>
+      <c r="H14" s="12" t="s">
+        <v>98</v>
+      </c>
+      <c r="I14" s="12" t="s">
+        <v>105</v>
+      </c>
+      <c r="J14" s="12" t="s">
+        <v>130</v>
+      </c>
+      <c r="K14" s="7" t="s">
+        <v>40</v>
+      </c>
+      <c r="L14" s="15" t="s">
+        <v>129</v>
+      </c>
+      <c r="M14" s="12" t="s">
+        <v>106</v>
+      </c>
+      <c r="N14" s="3" t="s">
+        <v>23</v>
+      </c>
+    </row>
+    <row r="15" spans="1:14" ht="31.2" x14ac:dyDescent="0.3">
+      <c r="A15" s="4" t="s">
+        <v>107</v>
+      </c>
+      <c r="B15" s="13" t="s">
+        <v>108</v>
+      </c>
+      <c r="C15" s="13" t="s">
+        <v>109</v>
+      </c>
+      <c r="D15" s="13" t="s">
+        <v>110</v>
+      </c>
+      <c r="E15" s="14" t="s">
+        <v>77</v>
+      </c>
+      <c r="F15" s="14" t="s">
+        <v>123</v>
+      </c>
+      <c r="G15" s="14" t="s">
+        <v>124</v>
+      </c>
+      <c r="H15" s="14"/>
+      <c r="I15" s="14" t="s">
+        <v>132</v>
+      </c>
+      <c r="J15" s="14" t="s">
+        <v>62</v>
+      </c>
+      <c r="K15" s="3" t="s">
+        <v>23</v>
+      </c>
+      <c r="L15" s="4" t="s">
+        <v>24</v>
+      </c>
+      <c r="M15" s="13" t="s">
         <v>133</v>
       </c>
-      <c r="O1" s="1" t="s">
-        <v>134</v>
+      <c r="N15" s="3" t="s">
+        <v>23</v>
       </c>
     </row>
-    <row r="2" spans="1:15" ht="30" x14ac:dyDescent="0.2">
-      <c r="A2" s="13" t="s">
-        <v>13</v>
-      </c>
-      <c r="B2" s="13" t="s">
-        <v>14</v>
-      </c>
-      <c r="C2" s="13" t="s">
-        <v>15</v>
-      </c>
-      <c r="D2" s="13" t="s">
-        <v>16</v>
-      </c>
-      <c r="E2" s="13" t="s">
-        <v>17</v>
-      </c>
-      <c r="F2" s="13" t="s">
-        <v>18</v>
-      </c>
-      <c r="G2" s="13" t="s">
-        <v>19</v>
-      </c>
-      <c r="H2" s="13" t="s">
-        <v>20</v>
-      </c>
-      <c r="I2" s="13" t="s">
-        <v>21</v>
-      </c>
-      <c r="J2" s="13" t="s">
-        <v>22</v>
-      </c>
-      <c r="K2" s="2" t="s">
-        <v>23</v>
-      </c>
-      <c r="L2" s="3" t="s">
+    <row r="16" spans="1:14" ht="31.2" x14ac:dyDescent="0.3">
+      <c r="A16" s="11" t="s">
+        <v>112</v>
+      </c>
+      <c r="B16" s="12" t="s">
+        <v>113</v>
+      </c>
+      <c r="C16" s="12" t="s">
+        <v>114</v>
+      </c>
+      <c r="D16" s="12" t="s">
+        <v>115</v>
+      </c>
+      <c r="E16" s="12" t="s">
+        <v>60</v>
+      </c>
+      <c r="F16" s="12" t="s">
+        <v>123</v>
+      </c>
+      <c r="G16" s="12" t="s">
+        <v>124</v>
+      </c>
+      <c r="H16" s="12"/>
+      <c r="I16" s="12" t="s">
+        <v>111</v>
+      </c>
+      <c r="J16" s="12" t="s">
+        <v>111</v>
+      </c>
+      <c r="K16" s="3" t="s">
+        <v>23</v>
+      </c>
+      <c r="L16" s="4" t="s">
         <v>24</v>
       </c>
-      <c r="M2" s="13" t="s">
-        <v>25</v>
-      </c>
-      <c r="N2" s="2" t="s">
-        <v>23</v>
-      </c>
-    </row>
-    <row r="3" spans="1:15" ht="30" x14ac:dyDescent="0.2">
-      <c r="A3" s="3" t="s">
-        <v>26</v>
-      </c>
-      <c r="B3" s="4" t="s">
-        <v>27</v>
-      </c>
-      <c r="C3" s="4" t="s">
-        <v>28</v>
-      </c>
-      <c r="D3" s="4" t="s">
-        <v>29</v>
-      </c>
-      <c r="E3" s="4" t="s">
-        <v>30</v>
-      </c>
-      <c r="F3" s="4" t="s">
-        <v>31</v>
-      </c>
-      <c r="G3" s="4" t="s">
-        <v>19</v>
-      </c>
-      <c r="H3" s="4" t="s">
-        <v>20</v>
-      </c>
-      <c r="I3" s="4" t="s">
-        <v>32</v>
-      </c>
-      <c r="J3" s="4" t="s">
-        <v>32</v>
-      </c>
-      <c r="K3" s="2" t="s">
-        <v>23</v>
-      </c>
-      <c r="L3" s="3" t="s">
-        <v>24</v>
-      </c>
-      <c r="M3" s="4" t="s">
-        <v>33</v>
-      </c>
-      <c r="N3" s="2" t="s">
-        <v>23</v>
-      </c>
-    </row>
-    <row r="4" spans="1:15" ht="57" x14ac:dyDescent="0.2">
-      <c r="A4" s="12" t="s">
-        <v>34</v>
-      </c>
-      <c r="B4" s="13" t="s">
-        <v>35</v>
-      </c>
-      <c r="C4" s="13" t="s">
-        <v>36</v>
-      </c>
-      <c r="D4" s="13" t="s">
-        <v>37</v>
-      </c>
-      <c r="E4" s="13" t="s">
-        <v>30</v>
-      </c>
-      <c r="F4" s="13" t="s">
-        <v>31</v>
-      </c>
-      <c r="G4" s="13" t="s">
-        <v>19</v>
-      </c>
-      <c r="H4" s="13" t="s">
-        <v>20</v>
-      </c>
-      <c r="I4" s="13" t="s">
-        <v>38</v>
-      </c>
-      <c r="J4" s="13" t="s">
-        <v>39</v>
-      </c>
-      <c r="K4" s="11" t="s">
-        <v>40</v>
-      </c>
-      <c r="L4" s="5" t="s">
-        <v>41</v>
-      </c>
-      <c r="M4" s="14" t="s">
-        <v>42</v>
-      </c>
-      <c r="N4" s="2" t="s">
-        <v>23</v>
-      </c>
-      <c r="O4" t="s">
-        <v>135</v>
-      </c>
-    </row>
-    <row r="5" spans="1:15" ht="57" x14ac:dyDescent="0.2">
-      <c r="A5" s="3" t="s">
-        <v>43</v>
-      </c>
-      <c r="B5" s="4" t="s">
-        <v>44</v>
-      </c>
-      <c r="C5" s="4" t="s">
-        <v>45</v>
-      </c>
-      <c r="D5" s="4" t="s">
-        <v>46</v>
-      </c>
-      <c r="E5" s="4" t="s">
-        <v>30</v>
-      </c>
-      <c r="F5" s="4" t="s">
-        <v>18</v>
-      </c>
-      <c r="G5" s="4" t="s">
-        <v>19</v>
-      </c>
-      <c r="H5" s="4" t="s">
-        <v>20</v>
-      </c>
-      <c r="I5" s="4" t="s">
-        <v>38</v>
-      </c>
-      <c r="J5" s="4" t="s">
-        <v>47</v>
-      </c>
-      <c r="K5" s="11" t="s">
-        <v>40</v>
-      </c>
-      <c r="L5" s="5" t="s">
-        <v>41</v>
-      </c>
-      <c r="M5" s="6" t="s">
-        <v>48</v>
-      </c>
-      <c r="N5" s="2" t="s">
-        <v>23</v>
-      </c>
-      <c r="O5" t="s">
-        <v>135</v>
-      </c>
-    </row>
-    <row r="6" spans="1:15" ht="60" x14ac:dyDescent="0.2">
-      <c r="A6" s="12" t="s">
-        <v>49</v>
-      </c>
-      <c r="B6" s="13" t="s">
-        <v>50</v>
-      </c>
-      <c r="C6" s="13" t="s">
-        <v>51</v>
-      </c>
-      <c r="D6" s="13" t="s">
-        <v>52</v>
-      </c>
-      <c r="E6" s="13" t="s">
-        <v>17</v>
-      </c>
-      <c r="F6" s="13" t="s">
-        <v>18</v>
-      </c>
-      <c r="G6" s="13" t="s">
-        <v>53</v>
-      </c>
-      <c r="H6" s="13" t="s">
-        <v>20</v>
-      </c>
-      <c r="I6" s="13" t="s">
-        <v>54</v>
-      </c>
-      <c r="J6" s="13" t="s">
-        <v>55</v>
-      </c>
-      <c r="K6" s="11" t="s">
-        <v>40</v>
-      </c>
-      <c r="L6" s="5" t="s">
-        <v>41</v>
-      </c>
-      <c r="M6" s="13" t="s">
-        <v>56</v>
-      </c>
-      <c r="N6" s="2" t="s">
-        <v>23</v>
-      </c>
-      <c r="O6" t="s">
-        <v>135</v>
-      </c>
-    </row>
-    <row r="7" spans="1:15" ht="30" x14ac:dyDescent="0.2">
-      <c r="A7" s="3" t="s">
-        <v>57</v>
-      </c>
-      <c r="B7" s="6" t="s">
-        <v>58</v>
-      </c>
-      <c r="C7" s="4" t="s">
-        <v>59</v>
-      </c>
-      <c r="D7" s="4" t="s">
-        <v>60</v>
-      </c>
-      <c r="E7" s="4" t="s">
-        <v>61</v>
-      </c>
-      <c r="F7" s="4" t="s">
-        <v>31</v>
-      </c>
-      <c r="G7" s="4" t="s">
-        <v>19</v>
-      </c>
-      <c r="H7" s="4" t="s">
-        <v>20</v>
-      </c>
-      <c r="I7" s="4" t="s">
-        <v>127</v>
-      </c>
-      <c r="J7" s="4" t="s">
-        <v>127</v>
-      </c>
-      <c r="K7" s="2" t="s">
-        <v>23</v>
-      </c>
-      <c r="L7" s="3" t="s">
-        <v>24</v>
-      </c>
-      <c r="M7" s="4" t="s">
-        <v>128</v>
-      </c>
-      <c r="N7" s="2" t="s">
-        <v>23</v>
-      </c>
-    </row>
-    <row r="8" spans="1:15" ht="30" x14ac:dyDescent="0.2">
-      <c r="A8" s="12" t="s">
-        <v>63</v>
-      </c>
-      <c r="B8" s="13" t="s">
-        <v>64</v>
-      </c>
-      <c r="C8" s="13" t="s">
-        <v>59</v>
-      </c>
-      <c r="D8" s="13" t="s">
-        <v>16</v>
-      </c>
-      <c r="E8" s="13" t="s">
-        <v>65</v>
-      </c>
-      <c r="F8" s="13" t="s">
-        <v>18</v>
-      </c>
-      <c r="G8" s="13" t="s">
-        <v>19</v>
-      </c>
-      <c r="H8" s="13" t="s">
-        <v>20</v>
-      </c>
-      <c r="I8" s="13" t="s">
-        <v>66</v>
-      </c>
-      <c r="J8" s="13" t="s">
-        <v>66</v>
-      </c>
-      <c r="K8" s="2" t="s">
-        <v>23</v>
-      </c>
-      <c r="L8" s="3" t="s">
-        <v>24</v>
-      </c>
-      <c r="M8" s="13" t="s">
-        <v>67</v>
-      </c>
-      <c r="N8" s="2" t="s">
-        <v>23</v>
-      </c>
-    </row>
-    <row r="9" spans="1:15" ht="45" x14ac:dyDescent="0.2">
-      <c r="A9" s="3" t="s">
-        <v>68</v>
-      </c>
-      <c r="B9" s="4" t="s">
-        <v>69</v>
-      </c>
-      <c r="C9" s="4" t="s">
-        <v>59</v>
-      </c>
-      <c r="D9" s="4" t="s">
-        <v>70</v>
-      </c>
-      <c r="E9" s="4" t="s">
-        <v>71</v>
-      </c>
-      <c r="F9" s="4" t="s">
-        <v>18</v>
-      </c>
-      <c r="G9" s="4" t="s">
-        <v>19</v>
-      </c>
-      <c r="H9" s="4" t="s">
-        <v>20</v>
-      </c>
-      <c r="I9" s="4" t="s">
-        <v>62</v>
-      </c>
-      <c r="J9" s="4" t="s">
-        <v>72</v>
-      </c>
-      <c r="K9" s="2" t="s">
-        <v>23</v>
-      </c>
-      <c r="L9" s="3" t="s">
-        <v>24</v>
-      </c>
-      <c r="M9" s="4" t="s">
-        <v>73</v>
-      </c>
-      <c r="N9" s="2" t="s">
-        <v>23</v>
-      </c>
-    </row>
-    <row r="10" spans="1:15" ht="45" x14ac:dyDescent="0.2">
-      <c r="A10" s="7" t="s">
-        <v>74</v>
-      </c>
-      <c r="B10" s="8" t="s">
-        <v>129</v>
-      </c>
-      <c r="C10" s="8" t="s">
-        <v>75</v>
-      </c>
-      <c r="D10" s="8" t="s">
-        <v>76</v>
-      </c>
-      <c r="E10" s="8" t="s">
-        <v>77</v>
-      </c>
-      <c r="F10" s="8" t="s">
-        <v>118</v>
-      </c>
-      <c r="G10" s="8" t="s">
-        <v>78</v>
-      </c>
-      <c r="H10" s="8" t="s">
-        <v>119</v>
-      </c>
-      <c r="I10" s="8" t="s">
-        <v>62</v>
-      </c>
-      <c r="J10" s="8" t="s">
-        <v>62</v>
-      </c>
-      <c r="K10" s="2" t="s">
-        <v>23</v>
-      </c>
-      <c r="L10" s="3" t="s">
-        <v>24</v>
-      </c>
-      <c r="M10" s="8" t="s">
-        <v>130</v>
-      </c>
-      <c r="N10" s="2" t="s">
-        <v>23</v>
-      </c>
-    </row>
-    <row r="11" spans="1:15" ht="45" x14ac:dyDescent="0.2">
-      <c r="A11" s="3" t="s">
-        <v>79</v>
-      </c>
-      <c r="B11" s="9" t="s">
-        <v>80</v>
-      </c>
-      <c r="C11" s="9" t="s">
-        <v>81</v>
-      </c>
-      <c r="D11" s="9" t="s">
-        <v>82</v>
-      </c>
-      <c r="E11" s="9" t="s">
-        <v>60</v>
-      </c>
-      <c r="F11" s="10" t="s">
-        <v>118</v>
-      </c>
-      <c r="G11" s="10" t="s">
-        <v>78</v>
-      </c>
-      <c r="H11" s="10" t="s">
-        <v>120</v>
-      </c>
-      <c r="I11" s="9" t="s">
-        <v>83</v>
-      </c>
-      <c r="J11" s="9" t="s">
-        <v>84</v>
-      </c>
-      <c r="K11" s="2" t="s">
-        <v>23</v>
-      </c>
-      <c r="L11" s="3" t="s">
-        <v>24</v>
-      </c>
-      <c r="M11" s="9" t="s">
-        <v>85</v>
-      </c>
-      <c r="N11" s="2" t="s">
-        <v>23</v>
-      </c>
-    </row>
-    <row r="12" spans="1:15" ht="60" x14ac:dyDescent="0.2">
-      <c r="A12" s="7" t="s">
-        <v>86</v>
-      </c>
-      <c r="B12" s="8" t="s">
-        <v>87</v>
-      </c>
-      <c r="C12" s="8" t="s">
-        <v>88</v>
-      </c>
-      <c r="D12" s="8" t="s">
-        <v>89</v>
-      </c>
-      <c r="E12" s="8" t="s">
-        <v>90</v>
-      </c>
-      <c r="F12" s="8" t="s">
-        <v>121</v>
-      </c>
-      <c r="G12" s="8" t="s">
-        <v>78</v>
-      </c>
-      <c r="H12" s="8" t="s">
-        <v>122</v>
-      </c>
-      <c r="I12" s="8" t="s">
-        <v>91</v>
-      </c>
-      <c r="J12" s="8" t="s">
-        <v>92</v>
-      </c>
-      <c r="K12" s="2" t="s">
-        <v>23</v>
-      </c>
-      <c r="L12" s="3" t="s">
-        <v>24</v>
-      </c>
-      <c r="M12" s="8" t="s">
-        <v>93</v>
-      </c>
-      <c r="N12" s="2" t="s">
-        <v>23</v>
-      </c>
-    </row>
-    <row r="13" spans="1:15" ht="30" x14ac:dyDescent="0.2">
-      <c r="A13" s="3" t="s">
-        <v>94</v>
-      </c>
-      <c r="B13" s="9" t="s">
-        <v>95</v>
-      </c>
-      <c r="C13" s="9" t="s">
-        <v>96</v>
-      </c>
-      <c r="D13" s="9" t="s">
-        <v>97</v>
-      </c>
-      <c r="E13" s="9" t="s">
-        <v>60</v>
-      </c>
-      <c r="F13" s="10" t="s">
-        <v>123</v>
-      </c>
-      <c r="G13" s="10" t="s">
-        <v>78</v>
-      </c>
-      <c r="H13" s="10" t="s">
-        <v>98</v>
-      </c>
-      <c r="I13" s="10" t="s">
-        <v>99</v>
-      </c>
-      <c r="J13" s="10" t="s">
-        <v>99</v>
-      </c>
-      <c r="K13" s="2" t="s">
-        <v>23</v>
-      </c>
-      <c r="L13" s="3" t="s">
-        <v>24</v>
-      </c>
-      <c r="M13" s="9" t="s">
-        <v>100</v>
-      </c>
-      <c r="N13" s="2" t="s">
-        <v>23</v>
-      </c>
-    </row>
-    <row r="14" spans="1:15" ht="45" x14ac:dyDescent="0.2">
-      <c r="A14" s="7" t="s">
-        <v>101</v>
-      </c>
-      <c r="B14" s="8" t="s">
-        <v>102</v>
-      </c>
-      <c r="C14" s="8" t="s">
-        <v>103</v>
-      </c>
-      <c r="D14" s="8" t="s">
-        <v>104</v>
-      </c>
-      <c r="E14" s="8" t="s">
-        <v>60</v>
-      </c>
-      <c r="F14" s="8" t="s">
-        <v>123</v>
-      </c>
-      <c r="G14" s="8" t="s">
-        <v>78</v>
-      </c>
-      <c r="H14" s="8" t="s">
-        <v>98</v>
-      </c>
-      <c r="I14" s="8" t="s">
-        <v>105</v>
-      </c>
-      <c r="J14" s="8" t="s">
-        <v>132</v>
-      </c>
-      <c r="K14" s="11" t="s">
-        <v>40</v>
-      </c>
-      <c r="L14" s="15" t="s">
-        <v>131</v>
-      </c>
-      <c r="M14" s="8" t="s">
-        <v>106</v>
-      </c>
-      <c r="N14" s="2" t="s">
-        <v>23</v>
-      </c>
-      <c r="O14" t="s">
-        <v>136</v>
-      </c>
-    </row>
-    <row r="15" spans="1:15" ht="75" x14ac:dyDescent="0.2">
-      <c r="A15" s="3" t="s">
-        <v>107</v>
-      </c>
-      <c r="B15" s="9" t="s">
-        <v>108</v>
-      </c>
-      <c r="C15" s="9" t="s">
-        <v>109</v>
-      </c>
-      <c r="D15" s="9" t="s">
-        <v>110</v>
-      </c>
-      <c r="E15" s="10" t="s">
-        <v>77</v>
-      </c>
-      <c r="F15" s="10" t="s">
-        <v>124</v>
-      </c>
-      <c r="G15" s="10" t="s">
-        <v>125</v>
-      </c>
-      <c r="H15" s="10"/>
-      <c r="I15" s="10" t="s">
-        <v>126</v>
-      </c>
-      <c r="J15" s="10" t="s">
-        <v>111</v>
-      </c>
-      <c r="K15" s="2" t="s">
-        <v>23</v>
-      </c>
-      <c r="L15" s="3" t="s">
-        <v>24</v>
-      </c>
-      <c r="M15" s="9" t="s">
-        <v>112</v>
-      </c>
-      <c r="N15" s="2" t="s">
-        <v>23</v>
-      </c>
-    </row>
-    <row r="16" spans="1:15" ht="30" x14ac:dyDescent="0.2">
-      <c r="A16" s="7" t="s">
-        <v>113</v>
-      </c>
-      <c r="B16" s="8" t="s">
-        <v>114</v>
-      </c>
-      <c r="C16" s="8" t="s">
-        <v>115</v>
-      </c>
-      <c r="D16" s="8" t="s">
+      <c r="M16" s="12" t="s">
         <v>116</v>
       </c>
-      <c r="E16" s="8" t="s">
-        <v>60</v>
-      </c>
-      <c r="F16" s="8" t="s">
-        <v>124</v>
-      </c>
-      <c r="G16" s="8" t="s">
-        <v>125</v>
-      </c>
-      <c r="H16" s="8"/>
-      <c r="I16" s="8" t="s">
-        <v>111</v>
-      </c>
-      <c r="J16" s="8" t="s">
-        <v>111</v>
-      </c>
-      <c r="K16" s="2" t="s">
-        <v>23</v>
-      </c>
-      <c r="L16" s="3" t="s">
-        <v>24</v>
-      </c>
-      <c r="M16" s="8" t="s">
-        <v>117</v>
-      </c>
-      <c r="N16" s="2" t="s">
+      <c r="N16" s="3" t="s">
         <v>23</v>
       </c>
     </row>
